--- a/artfynd/A 1719-2025 artfynd.xlsx
+++ b/artfynd/A 1719-2025 artfynd.xlsx
@@ -903,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122363018</v>
+        <v>122363016</v>
       </c>
       <c r="B4" t="n">
         <v>106462</v>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>715152</v>
+        <v>715199</v>
       </c>
       <c r="R4" t="n">
-        <v>6381113</v>
+        <v>6381142</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122363020</v>
+        <v>122363017</v>
       </c>
       <c r="B6" t="n">
-        <v>99703</v>
+        <v>106462</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,47 +1139,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>783</v>
+        <v>221849</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>715124</v>
+        <v>715169</v>
       </c>
       <c r="R6" t="n">
-        <v>6381128</v>
+        <v>6381129</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1216,7 +1207,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Tre strån.</t>
+          <t>Även spridd.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,7 +1221,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, död ved, i svacka mellan kalkryggar.</t>
+          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1248,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122363017</v>
+        <v>122363020</v>
       </c>
       <c r="B7" t="n">
-        <v>106462</v>
+        <v>99703</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,38 +1251,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221849</v>
+        <v>783</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>715169</v>
+        <v>715124</v>
       </c>
       <c r="R7" t="n">
-        <v>6381129</v>
+        <v>6381128</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Även spridd.</t>
+          <t>Tre strån.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
+          <t>Kalkbarrskog, död ved, i svacka mellan kalkryggar.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1709,7 +1709,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122363016</v>
+        <v>122363018</v>
       </c>
       <c r="B11" t="n">
         <v>106462</v>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>715199</v>
+        <v>715152</v>
       </c>
       <c r="R11" t="n">
-        <v>6381142</v>
+        <v>6381113</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 1719-2025 artfynd.xlsx
+++ b/artfynd/A 1719-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122362584</v>
+        <v>122363016</v>
       </c>
       <c r="B2" t="n">
-        <v>57390</v>
+        <v>106472</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,46 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221849</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>715124</v>
+        <v>715199</v>
       </c>
       <c r="R2" t="n">
-        <v>6381128</v>
+        <v>6381142</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Hackspår efter födosök i gran.</t>
+          <t>Även spridd.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,6 +766,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -791,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122363027</v>
+        <v>122363059</v>
       </c>
       <c r="B3" t="n">
-        <v>100441</v>
+        <v>106472</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>221849</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>715165</v>
+        <v>715216</v>
       </c>
       <c r="R3" t="n">
-        <v>6381230</v>
+        <v>6381161</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,7 +867,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Även spridd.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,7 +881,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -903,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122363016</v>
+        <v>122362584</v>
       </c>
       <c r="B4" t="n">
-        <v>106462</v>
+        <v>57390</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,37 +915,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221849</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>715199</v>
+        <v>715124</v>
       </c>
       <c r="R4" t="n">
-        <v>6381142</v>
+        <v>6381128</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +988,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Även spridd.</t>
+          <t>Hackspår efter födosök i gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,11 +999,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122363059</v>
+        <v>122363019</v>
       </c>
       <c r="B5" t="n">
-        <v>106462</v>
+        <v>106472</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>715216</v>
+        <v>715140</v>
       </c>
       <c r="R5" t="n">
-        <v>6381161</v>
+        <v>6381111</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1130,7 +1130,7 @@
         <v>122363017</v>
       </c>
       <c r="B6" t="n">
-        <v>106462</v>
+        <v>106472</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1239,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122363020</v>
+        <v>122363029</v>
       </c>
       <c r="B7" t="n">
-        <v>99703</v>
+        <v>105846</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,25 +1251,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>783</v>
+        <v>220785</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>715124</v>
+        <v>715165</v>
       </c>
       <c r="R7" t="n">
-        <v>6381128</v>
+        <v>6381230</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1326,11 +1326,6 @@
           <t>2025-01-27</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Tre strån.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1342,7 +1337,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, död ved, i svacka mellan kalkryggar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1360,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122363019</v>
+        <v>122363027</v>
       </c>
       <c r="B8" t="n">
-        <v>106462</v>
+        <v>100451</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1372,25 +1367,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221849</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1400,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715140</v>
+        <v>715165</v>
       </c>
       <c r="R8" t="n">
-        <v>6381111</v>
+        <v>6381230</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1440,7 +1435,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Även spridd.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1454,7 +1449,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1472,10 +1467,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122363029</v>
+        <v>122363018</v>
       </c>
       <c r="B9" t="n">
-        <v>105836</v>
+        <v>106472</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1484,20 +1479,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220785</v>
+        <v>221849</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1505,26 +1500,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>715165</v>
+        <v>715152</v>
       </c>
       <c r="R9" t="n">
-        <v>6381230</v>
+        <v>6381113</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1559,6 +1545,11 @@
           <t>2025-01-27</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Även spridd.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1570,7 +1561,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1588,10 +1579,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122363025</v>
+        <v>122363020</v>
       </c>
       <c r="B10" t="n">
-        <v>98153</v>
+        <v>99713</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,25 +1591,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1631,21 +1622,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>715113</v>
+        <v>715124</v>
       </c>
       <c r="R10" t="n">
-        <v>6381204</v>
+        <v>6381128</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1680,6 +1666,11 @@
           <t>2025-01-27</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Tre strån.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1691,7 +1682,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, död ved, i svacka mellan kalkryggar.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1709,10 +1700,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122363018</v>
+        <v>122363025</v>
       </c>
       <c r="B11" t="n">
-        <v>106462</v>
+        <v>98163</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,38 +1712,52 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221849</v>
+        <v>219798</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>715152</v>
+        <v>715113</v>
       </c>
       <c r="R11" t="n">
-        <v>6381113</v>
+        <v>6381204</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1787,11 +1792,6 @@
           <t>2025-01-27</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Även spridd.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 1719-2025 artfynd.xlsx
+++ b/artfynd/A 1719-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122363016</v>
+        <v>122363018</v>
       </c>
       <c r="B2" t="n">
         <v>106472</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>715199</v>
+        <v>715152</v>
       </c>
       <c r="R2" t="n">
-        <v>6381142</v>
+        <v>6381113</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122363059</v>
+        <v>122363016</v>
       </c>
       <c r="B3" t="n">
         <v>106472</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>715216</v>
+        <v>715199</v>
       </c>
       <c r="R3" t="n">
-        <v>6381161</v>
+        <v>6381142</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122362584</v>
+        <v>122363029</v>
       </c>
       <c r="B4" t="n">
-        <v>57390</v>
+        <v>105846</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220785</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,9 +937,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -948,13 +948,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>715124</v>
+        <v>715165</v>
       </c>
       <c r="R4" t="n">
-        <v>6381128</v>
+        <v>6381230</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,11 +986,6 @@
           <t>2025-01-27</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Hackspår efter födosök i gran.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -999,6 +994,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122363019</v>
+        <v>122363027</v>
       </c>
       <c r="B5" t="n">
-        <v>106472</v>
+        <v>100451</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,25 +1027,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221849</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>715140</v>
+        <v>715165</v>
       </c>
       <c r="R5" t="n">
-        <v>6381111</v>
+        <v>6381230</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Även spridd.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122363017</v>
+        <v>122363025</v>
       </c>
       <c r="B6" t="n">
-        <v>106472</v>
+        <v>98163</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,38 +1139,52 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221849</v>
+        <v>219798</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>715169</v>
+        <v>715113</v>
       </c>
       <c r="R6" t="n">
-        <v>6381129</v>
+        <v>6381204</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1205,11 +1219,6 @@
           <t>2025-01-27</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Även spridd.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1221,7 +1230,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1239,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122363029</v>
+        <v>122363017</v>
       </c>
       <c r="B7" t="n">
-        <v>105846</v>
+        <v>106472</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,20 +1260,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220785</v>
+        <v>221849</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1272,26 +1281,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>715165</v>
+        <v>715169</v>
       </c>
       <c r="R7" t="n">
-        <v>6381230</v>
+        <v>6381129</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1326,6 +1326,11 @@
           <t>2025-01-27</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Även spridd.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1337,7 +1342,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1355,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122363027</v>
+        <v>122362584</v>
       </c>
       <c r="B8" t="n">
-        <v>100451</v>
+        <v>57390</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,41 +1372,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715165</v>
+        <v>715124</v>
       </c>
       <c r="R8" t="n">
-        <v>6381230</v>
+        <v>6381128</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1435,7 +1449,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Hackspår efter födosök i gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1446,11 +1460,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1467,7 +1476,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122363018</v>
+        <v>122363019</v>
       </c>
       <c r="B9" t="n">
         <v>106472</v>
@@ -1507,10 +1516,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>715152</v>
+        <v>715140</v>
       </c>
       <c r="R9" t="n">
-        <v>6381113</v>
+        <v>6381111</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1579,10 +1588,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122363020</v>
+        <v>122363059</v>
       </c>
       <c r="B10" t="n">
-        <v>99713</v>
+        <v>106472</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1591,47 +1600,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>783</v>
+        <v>221849</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>715124</v>
+        <v>715216</v>
       </c>
       <c r="R10" t="n">
-        <v>6381128</v>
+        <v>6381161</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Tre strån.</t>
+          <t>Även spridd.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, död ved, i svacka mellan kalkryggar.</t>
+          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122363025</v>
+        <v>122363020</v>
       </c>
       <c r="B11" t="n">
-        <v>98163</v>
+        <v>99713</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1712,25 +1712,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1743,21 +1743,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>715113</v>
+        <v>715124</v>
       </c>
       <c r="R11" t="n">
-        <v>6381204</v>
+        <v>6381128</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1792,6 +1787,11 @@
           <t>2025-01-27</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Tre strån.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, död ved, i svacka mellan kalkryggar.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 1719-2025 artfynd.xlsx
+++ b/artfynd/A 1719-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122363018</v>
+        <v>122363059</v>
       </c>
       <c r="B2" t="n">
-        <v>106472</v>
+        <v>106485</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>715152</v>
+        <v>715216</v>
       </c>
       <c r="R2" t="n">
-        <v>6381113</v>
+        <v>6381161</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122363016</v>
+        <v>122363017</v>
       </c>
       <c r="B3" t="n">
-        <v>106472</v>
+        <v>106485</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>715199</v>
+        <v>715169</v>
       </c>
       <c r="R3" t="n">
-        <v>6381142</v>
+        <v>6381129</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122363029</v>
+        <v>122363025</v>
       </c>
       <c r="B4" t="n">
-        <v>105846</v>
+        <v>98175</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -942,16 +942,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>715165</v>
+        <v>715113</v>
       </c>
       <c r="R4" t="n">
-        <v>6381230</v>
+        <v>6381204</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1015,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122363027</v>
+        <v>122362584</v>
       </c>
       <c r="B5" t="n">
-        <v>100451</v>
+        <v>57395</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,41 +1032,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>715165</v>
+        <v>715124</v>
       </c>
       <c r="R5" t="n">
-        <v>6381230</v>
+        <v>6381128</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,7 +1109,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Hackspår efter födosök i gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,11 +1120,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1127,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122363025</v>
+        <v>122363018</v>
       </c>
       <c r="B6" t="n">
-        <v>98163</v>
+        <v>106485</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,52 +1148,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219798</v>
+        <v>221849</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>715113</v>
+        <v>715152</v>
       </c>
       <c r="R6" t="n">
-        <v>6381204</v>
+        <v>6381113</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1219,6 +1214,11 @@
           <t>2025-01-27</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Även spridd.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1248,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122363017</v>
+        <v>122363020</v>
       </c>
       <c r="B7" t="n">
-        <v>106472</v>
+        <v>99725</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,38 +1260,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221849</v>
+        <v>783</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>715169</v>
+        <v>715124</v>
       </c>
       <c r="R7" t="n">
-        <v>6381129</v>
+        <v>6381128</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1328,7 +1337,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Även spridd.</t>
+          <t>Tre strån.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,7 +1351,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
+          <t>Kalkbarrskog, död ved, i svacka mellan kalkryggar.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1360,10 +1369,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122362584</v>
+        <v>122363016</v>
       </c>
       <c r="B8" t="n">
-        <v>57390</v>
+        <v>106485</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,46 +1385,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>221849</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715124</v>
+        <v>715199</v>
       </c>
       <c r="R8" t="n">
-        <v>6381128</v>
+        <v>6381142</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Hackspår efter födosök i gran.</t>
+          <t>Även spridd.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1460,6 +1460,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1476,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122363019</v>
+        <v>122363029</v>
       </c>
       <c r="B9" t="n">
-        <v>106472</v>
+        <v>105859</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1488,20 +1493,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221849</v>
+        <v>220785</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1509,17 +1514,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>715140</v>
+        <v>715165</v>
       </c>
       <c r="R9" t="n">
-        <v>6381111</v>
+        <v>6381230</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1554,11 +1568,6 @@
           <t>2025-01-27</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Även spridd.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1570,7 +1579,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1588,10 +1597,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122363059</v>
+        <v>122363019</v>
       </c>
       <c r="B10" t="n">
-        <v>106472</v>
+        <v>106485</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1628,10 +1637,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>715216</v>
+        <v>715140</v>
       </c>
       <c r="R10" t="n">
-        <v>6381161</v>
+        <v>6381111</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1700,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122363020</v>
+        <v>122363027</v>
       </c>
       <c r="B11" t="n">
-        <v>99713</v>
+        <v>100463</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1712,47 +1721,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>783</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>715124</v>
+        <v>715165</v>
       </c>
       <c r="R11" t="n">
-        <v>6381128</v>
+        <v>6381230</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Tre strån.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, död ved, i svacka mellan kalkryggar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 1719-2025 artfynd.xlsx
+++ b/artfynd/A 1719-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122363059</v>
+        <v>122363020</v>
       </c>
       <c r="B2" t="n">
-        <v>106485</v>
+        <v>99730</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221849</v>
+        <v>783</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>715216</v>
+        <v>715124</v>
       </c>
       <c r="R2" t="n">
-        <v>6381161</v>
+        <v>6381128</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +764,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Även spridd.</t>
+          <t>Tre strån.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,7 +778,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
+          <t>Kalkbarrskog, död ved, i svacka mellan kalkryggar.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -787,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122363017</v>
+        <v>122363016</v>
       </c>
       <c r="B3" t="n">
-        <v>106485</v>
+        <v>106490</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>715169</v>
+        <v>715199</v>
       </c>
       <c r="R3" t="n">
-        <v>6381129</v>
+        <v>6381142</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -902,7 +911,7 @@
         <v>122363025</v>
       </c>
       <c r="B4" t="n">
-        <v>98175</v>
+        <v>98180</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1020,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122362584</v>
+        <v>122363027</v>
       </c>
       <c r="B5" t="n">
-        <v>57395</v>
+        <v>100468</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,50 +1041,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>715124</v>
+        <v>715165</v>
       </c>
       <c r="R5" t="n">
-        <v>6381128</v>
+        <v>6381230</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Hackspår efter födosök i gran.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,6 +1120,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1136,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122363018</v>
+        <v>122363029</v>
       </c>
       <c r="B6" t="n">
-        <v>106485</v>
+        <v>105864</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,20 +1153,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221849</v>
+        <v>220785</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1169,17 +1174,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>715152</v>
+        <v>715165</v>
       </c>
       <c r="R6" t="n">
-        <v>6381113</v>
+        <v>6381230</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1214,11 +1228,6 @@
           <t>2025-01-27</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Även spridd.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1230,7 +1239,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1248,10 +1257,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122363020</v>
+        <v>122363019</v>
       </c>
       <c r="B7" t="n">
-        <v>99725</v>
+        <v>106490</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,47 +1269,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>783</v>
+        <v>221849</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>715124</v>
+        <v>715140</v>
       </c>
       <c r="R7" t="n">
-        <v>6381128</v>
+        <v>6381111</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Tre strån.</t>
+          <t>Även spridd.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, död ved, i svacka mellan kalkryggar.</t>
+          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1369,10 +1369,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122363016</v>
+        <v>122363018</v>
       </c>
       <c r="B8" t="n">
-        <v>106485</v>
+        <v>106490</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715199</v>
+        <v>715152</v>
       </c>
       <c r="R8" t="n">
-        <v>6381142</v>
+        <v>6381113</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1481,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122363029</v>
+        <v>122363059</v>
       </c>
       <c r="B9" t="n">
-        <v>105859</v>
+        <v>106490</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1493,20 +1493,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220785</v>
+        <v>221849</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1514,26 +1514,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>715165</v>
+        <v>715216</v>
       </c>
       <c r="R9" t="n">
-        <v>6381230</v>
+        <v>6381161</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1568,6 +1559,11 @@
           <t>2025-01-27</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Även spridd.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1579,7 +1575,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1597,10 +1593,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122363019</v>
+        <v>122363017</v>
       </c>
       <c r="B10" t="n">
-        <v>106485</v>
+        <v>106490</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1637,10 +1633,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>715140</v>
+        <v>715169</v>
       </c>
       <c r="R10" t="n">
-        <v>6381111</v>
+        <v>6381129</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1709,10 +1705,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122363027</v>
+        <v>122362584</v>
       </c>
       <c r="B11" t="n">
-        <v>100463</v>
+        <v>57395</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,41 +1717,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>715165</v>
+        <v>715124</v>
       </c>
       <c r="R11" t="n">
-        <v>6381230</v>
+        <v>6381128</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1789,7 +1794,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Hackspår efter födosök i gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,11 +1805,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">

--- a/artfynd/A 1719-2025 artfynd.xlsx
+++ b/artfynd/A 1719-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122363020</v>
+        <v>122363027</v>
       </c>
       <c r="B2" t="n">
-        <v>99730</v>
+        <v>100477</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,33 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>783</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Skogskorn</t>
-        </is>
+        <v>222498</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>715124</v>
+        <v>715165</v>
       </c>
       <c r="R2" t="n">
-        <v>6381128</v>
+        <v>6381230</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -764,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Tre strån.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,7 +764,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, död ved, i svacka mellan kalkryggar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -796,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122363016</v>
+        <v>122363019</v>
       </c>
       <c r="B3" t="n">
-        <v>106490</v>
+        <v>106499</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -814,11 +800,6 @@
       <c r="E3" t="n">
         <v>221849</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Backtimjan</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Thymus serpyllum</t>
@@ -836,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>715199</v>
+        <v>715140</v>
       </c>
       <c r="R3" t="n">
-        <v>6381142</v>
+        <v>6381111</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -908,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122363025</v>
+        <v>122363018</v>
       </c>
       <c r="B4" t="n">
-        <v>98180</v>
+        <v>106499</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,52 +901,33 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Skogsknipprot</t>
-        </is>
+        <v>221849</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>715113</v>
+        <v>715152</v>
       </c>
       <c r="R4" t="n">
-        <v>6381204</v>
+        <v>6381113</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1000,6 +962,11 @@
           <t>2025-01-27</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Även spridd.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1011,7 +978,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1029,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122363027</v>
+        <v>122362584</v>
       </c>
       <c r="B5" t="n">
-        <v>100468</v>
+        <v>57395</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,41 +1008,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>715165</v>
+        <v>715124</v>
       </c>
       <c r="R5" t="n">
-        <v>6381230</v>
+        <v>6381128</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,7 +1080,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Hackspår efter födosök i gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,11 +1091,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1141,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122363029</v>
+        <v>122363025</v>
       </c>
       <c r="B6" t="n">
-        <v>105864</v>
+        <v>98189</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,25 +1119,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220785</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Ask</t>
-        </is>
+        <v>219798</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1184,16 +1145,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>715165</v>
+        <v>715113</v>
       </c>
       <c r="R6" t="n">
-        <v>6381230</v>
+        <v>6381204</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1257,10 +1223,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122363019</v>
+        <v>122363016</v>
       </c>
       <c r="B7" t="n">
-        <v>106490</v>
+        <v>106499</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,11 +1241,6 @@
       <c r="E7" t="n">
         <v>221849</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Backtimjan</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Thymus serpyllum</t>
@@ -1297,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>715140</v>
+        <v>715199</v>
       </c>
       <c r="R7" t="n">
-        <v>6381111</v>
+        <v>6381142</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1369,10 +1330,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122363018</v>
+        <v>122363020</v>
       </c>
       <c r="B8" t="n">
-        <v>106490</v>
+        <v>99739</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,38 +1342,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221849</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Backtimjan</t>
-        </is>
+        <v>783</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715152</v>
+        <v>715124</v>
       </c>
       <c r="R8" t="n">
-        <v>6381113</v>
+        <v>6381128</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1449,7 +1414,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Även spridd.</t>
+          <t>Tre strån.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,7 +1428,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
+          <t>Kalkbarrskog, död ved, i svacka mellan kalkryggar.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1484,7 +1449,7 @@
         <v>122363059</v>
       </c>
       <c r="B9" t="n">
-        <v>106490</v>
+        <v>106499</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,11 +1463,6 @@
       </c>
       <c r="E9" t="n">
         <v>221849</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Backtimjan</t>
-        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1596,7 +1556,7 @@
         <v>122363017</v>
       </c>
       <c r="B10" t="n">
-        <v>106490</v>
+        <v>106499</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,11 +1570,6 @@
       </c>
       <c r="E10" t="n">
         <v>221849</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Backtimjan</t>
-        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1705,10 +1660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122362584</v>
+        <v>122363029</v>
       </c>
       <c r="B11" t="n">
-        <v>57395</v>
+        <v>105873</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1717,25 +1672,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>220785</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1743,9 +1693,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1754,13 +1704,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>715124</v>
+        <v>715165</v>
       </c>
       <c r="R11" t="n">
-        <v>6381128</v>
+        <v>6381230</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1792,11 +1742,6 @@
           <t>2025-01-27</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Hackspår efter födosök i gran.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1805,6 +1750,11 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">

--- a/artfynd/A 1719-2025 artfynd.xlsx
+++ b/artfynd/A 1719-2025 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122363018</v>
+        <v>122362584</v>
       </c>
       <c r="B4" t="n">
-        <v>106499</v>
+        <v>57395</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,32 +905,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221849</v>
+        <v>100049</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>715152</v>
+        <v>715124</v>
       </c>
       <c r="R4" t="n">
-        <v>6381113</v>
+        <v>6381128</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,7 +973,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Även spridd.</t>
+          <t>Hackspår efter födosök i gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -975,11 +984,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -996,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122362584</v>
+        <v>122363018</v>
       </c>
       <c r="B5" t="n">
-        <v>57395</v>
+        <v>106499</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,41 +1016,32 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>221849</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>715124</v>
+        <v>715152</v>
       </c>
       <c r="R5" t="n">
-        <v>6381128</v>
+        <v>6381113</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,7 +1075,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Hackspår efter födosök i gran.</t>
+          <t>Även spridd.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,6 +1086,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">

--- a/artfynd/A 1719-2025 artfynd.xlsx
+++ b/artfynd/A 1719-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122363027</v>
+        <v>122363017</v>
       </c>
       <c r="B2" t="n">
-        <v>100477</v>
+        <v>106512</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>221849</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>715165</v>
+        <v>715169</v>
       </c>
       <c r="R2" t="n">
-        <v>6381230</v>
+        <v>6381129</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Även spridd.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,7 +769,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -782,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122363019</v>
+        <v>122363020</v>
       </c>
       <c r="B3" t="n">
-        <v>106499</v>
+        <v>99752</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,33 +799,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221849</v>
+        <v>783</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skogskorn</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>715140</v>
+        <v>715124</v>
       </c>
       <c r="R3" t="n">
-        <v>6381111</v>
+        <v>6381128</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,7 +876,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Även spridd.</t>
+          <t>Tre strån.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,7 +890,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
+          <t>Kalkbarrskog, död ved, i svacka mellan kalkryggar.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -889,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122362584</v>
+        <v>122363016</v>
       </c>
       <c r="B4" t="n">
-        <v>57395</v>
+        <v>106512</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,41 +924,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>221849</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>715124</v>
+        <v>715199</v>
       </c>
       <c r="R4" t="n">
-        <v>6381128</v>
+        <v>6381142</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,7 +988,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Hackspår efter födosök i gran.</t>
+          <t>Även spridd.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,6 +999,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1000,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122363018</v>
+        <v>122363029</v>
       </c>
       <c r="B5" t="n">
-        <v>106499</v>
+        <v>105886</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,15 +1032,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221849</v>
+        <v>220785</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1028,17 +1053,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>715152</v>
+        <v>715165</v>
       </c>
       <c r="R5" t="n">
-        <v>6381113</v>
+        <v>6381230</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1073,11 +1107,6 @@
           <t>2025-01-27</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Även spridd.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1089,7 +1118,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1107,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122363025</v>
+        <v>122363027</v>
       </c>
       <c r="B6" t="n">
-        <v>98189</v>
+        <v>100490</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,43 +1152,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219798</v>
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>715113</v>
+        <v>715165</v>
       </c>
       <c r="R6" t="n">
-        <v>6381204</v>
+        <v>6381230</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1192,6 +1212,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-01-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122363016</v>
+        <v>122363018</v>
       </c>
       <c r="B7" t="n">
-        <v>106499</v>
+        <v>106512</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,6 +1266,11 @@
       <c r="E7" t="n">
         <v>221849</v>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Thymus serpyllum</t>
@@ -1258,10 +1288,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>715199</v>
+        <v>715152</v>
       </c>
       <c r="R7" t="n">
-        <v>6381142</v>
+        <v>6381113</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1330,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122363020</v>
+        <v>122363019</v>
       </c>
       <c r="B8" t="n">
-        <v>99739</v>
+        <v>106512</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1342,42 +1372,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>783</v>
+        <v>221849</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715124</v>
+        <v>715140</v>
       </c>
       <c r="R8" t="n">
-        <v>6381128</v>
+        <v>6381111</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1414,7 +1440,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Tre strån.</t>
+          <t>Även spridd.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1428,7 +1454,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, död ved, i svacka mellan kalkryggar.</t>
+          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1446,10 +1472,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122363059</v>
+        <v>122363025</v>
       </c>
       <c r="B9" t="n">
-        <v>106499</v>
+        <v>98202</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1458,33 +1484,52 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221849</v>
+        <v>219798</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>715216</v>
+        <v>715113</v>
       </c>
       <c r="R9" t="n">
-        <v>6381161</v>
+        <v>6381204</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1519,11 +1564,6 @@
           <t>2025-01-27</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Även spridd.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1535,7 +1575,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1553,10 +1593,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122363017</v>
+        <v>122362584</v>
       </c>
       <c r="B10" t="n">
-        <v>106499</v>
+        <v>57399</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1569,32 +1609,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221849</v>
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>715169</v>
+        <v>715124</v>
       </c>
       <c r="R10" t="n">
-        <v>6381129</v>
+        <v>6381128</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1628,7 +1682,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Även spridd.</t>
+          <t>Hackspår efter födosök i gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1639,11 +1693,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1660,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122363029</v>
+        <v>122363059</v>
       </c>
       <c r="B11" t="n">
-        <v>105873</v>
+        <v>106512</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1672,15 +1721,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220785</v>
+        <v>221849</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1688,26 +1742,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>715165</v>
+        <v>715216</v>
       </c>
       <c r="R11" t="n">
-        <v>6381230</v>
+        <v>6381161</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1742,6 +1787,11 @@
           <t>2025-01-27</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Även spridd.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1753,7 +1803,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 1719-2025 artfynd.xlsx
+++ b/artfynd/A 1719-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122363017</v>
+        <v>122363027</v>
       </c>
       <c r="B2" t="n">
-        <v>106512</v>
+        <v>100503</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221849</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>715169</v>
+        <v>715165</v>
       </c>
       <c r="R2" t="n">
-        <v>6381129</v>
+        <v>6381230</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Även spridd.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,7 +769,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122363020</v>
+        <v>122363019</v>
       </c>
       <c r="B3" t="n">
-        <v>99752</v>
+        <v>106525</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,47 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>783</v>
+        <v>221849</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>715124</v>
+        <v>715140</v>
       </c>
       <c r="R3" t="n">
-        <v>6381128</v>
+        <v>6381111</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -876,7 +867,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Tre strån.</t>
+          <t>Även spridd.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +881,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, död ved, i svacka mellan kalkryggar.</t>
+          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -908,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122363016</v>
+        <v>122363025</v>
       </c>
       <c r="B4" t="n">
-        <v>106512</v>
+        <v>98215</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,38 +911,52 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221849</v>
+        <v>219798</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>715199</v>
+        <v>715113</v>
       </c>
       <c r="R4" t="n">
-        <v>6381142</v>
+        <v>6381204</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,11 +991,6 @@
           <t>2025-01-27</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Även spridd.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122363029</v>
+        <v>122363018</v>
       </c>
       <c r="B5" t="n">
-        <v>105886</v>
+        <v>106525</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,20 +1032,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220785</v>
+        <v>221849</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1053,26 +1053,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>715165</v>
+        <v>715152</v>
       </c>
       <c r="R5" t="n">
-        <v>6381230</v>
+        <v>6381113</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1107,6 +1098,11 @@
           <t>2025-01-27</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Även spridd.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1118,7 +1114,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1136,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122363027</v>
+        <v>122362584</v>
       </c>
       <c r="B6" t="n">
-        <v>100490</v>
+        <v>57399</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,41 +1144,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>715165</v>
+        <v>715124</v>
       </c>
       <c r="R6" t="n">
-        <v>6381230</v>
+        <v>6381128</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,7 +1221,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Hackspår efter födosök i gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,11 +1232,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1248,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122363018</v>
+        <v>122363029</v>
       </c>
       <c r="B7" t="n">
-        <v>106512</v>
+        <v>105899</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,20 +1260,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221849</v>
+        <v>220785</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1281,17 +1281,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>715152</v>
+        <v>715165</v>
       </c>
       <c r="R7" t="n">
-        <v>6381113</v>
+        <v>6381230</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1326,11 +1335,6 @@
           <t>2025-01-27</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Även spridd.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1342,7 +1346,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1360,10 +1364,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122363019</v>
+        <v>122363059</v>
       </c>
       <c r="B8" t="n">
-        <v>106512</v>
+        <v>106525</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1400,10 +1404,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715140</v>
+        <v>715216</v>
       </c>
       <c r="R8" t="n">
-        <v>6381111</v>
+        <v>6381161</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1472,10 +1476,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122363025</v>
+        <v>122363020</v>
       </c>
       <c r="B9" t="n">
-        <v>98202</v>
+        <v>99765</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1484,25 +1488,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1515,21 +1519,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>715113</v>
+        <v>715124</v>
       </c>
       <c r="R9" t="n">
-        <v>6381204</v>
+        <v>6381128</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1564,6 +1563,11 @@
           <t>2025-01-27</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Tre strån.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1575,7 +1579,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, död ved, i svacka mellan kalkryggar.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1593,10 +1597,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122362584</v>
+        <v>122363017</v>
       </c>
       <c r="B10" t="n">
-        <v>57399</v>
+        <v>106525</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1609,46 +1613,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>221849</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>715124</v>
+        <v>715169</v>
       </c>
       <c r="R10" t="n">
-        <v>6381128</v>
+        <v>6381129</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1682,7 +1677,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Hackspår efter födosök i gran.</t>
+          <t>Även spridd.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,6 +1688,11 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1709,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122363059</v>
+        <v>122363016</v>
       </c>
       <c r="B11" t="n">
-        <v>106512</v>
+        <v>106525</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>715216</v>
+        <v>715199</v>
       </c>
       <c r="R11" t="n">
-        <v>6381161</v>
+        <v>6381142</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 1719-2025 artfynd.xlsx
+++ b/artfynd/A 1719-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122363027</v>
+        <v>122363019</v>
       </c>
       <c r="B2" t="n">
-        <v>100503</v>
+        <v>106525</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>221849</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>715165</v>
+        <v>715140</v>
       </c>
       <c r="R2" t="n">
-        <v>6381230</v>
+        <v>6381111</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Även spridd.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,7 +769,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122363019</v>
+        <v>122363059</v>
       </c>
       <c r="B3" t="n">
         <v>106525</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>715140</v>
+        <v>715216</v>
       </c>
       <c r="R3" t="n">
-        <v>6381111</v>
+        <v>6381161</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122363025</v>
+        <v>122363018</v>
       </c>
       <c r="B4" t="n">
-        <v>98215</v>
+        <v>106525</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,52 +911,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>221849</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>715113</v>
+        <v>715152</v>
       </c>
       <c r="R4" t="n">
-        <v>6381204</v>
+        <v>6381113</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -991,6 +977,11 @@
           <t>2025-01-27</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Även spridd.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1002,7 +993,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1020,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122363018</v>
+        <v>122363020</v>
       </c>
       <c r="B5" t="n">
-        <v>106525</v>
+        <v>99765</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,38 +1023,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221849</v>
+        <v>783</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>715152</v>
+        <v>715124</v>
       </c>
       <c r="R5" t="n">
-        <v>6381113</v>
+        <v>6381128</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Även spridd.</t>
+          <t>Tre strån.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
+          <t>Kalkbarrskog, död ved, i svacka mellan kalkryggar.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1248,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122363029</v>
+        <v>122363027</v>
       </c>
       <c r="B7" t="n">
-        <v>105899</v>
+        <v>100503</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,37 +1260,28 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220785</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
@@ -1333,6 +1324,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-27</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122363059</v>
+        <v>122363025</v>
       </c>
       <c r="B8" t="n">
-        <v>106525</v>
+        <v>98215</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,38 +1372,52 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221849</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715216</v>
+        <v>715113</v>
       </c>
       <c r="R8" t="n">
-        <v>6381161</v>
+        <v>6381204</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1442,11 +1452,6 @@
           <t>2025-01-27</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Även spridd.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1458,7 +1463,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1476,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122363020</v>
+        <v>122363029</v>
       </c>
       <c r="B9" t="n">
-        <v>99765</v>
+        <v>105899</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1488,25 +1493,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>783</v>
+        <v>220785</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1525,10 +1530,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>715124</v>
+        <v>715165</v>
       </c>
       <c r="R9" t="n">
-        <v>6381128</v>
+        <v>6381230</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1563,11 +1568,6 @@
           <t>2025-01-27</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Tre strån.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, död ved, i svacka mellan kalkryggar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 1719-2025 artfynd.xlsx
+++ b/artfynd/A 1719-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122363019</v>
+        <v>122363029</v>
       </c>
       <c r="B2" t="n">
-        <v>106525</v>
+        <v>105902</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221849</v>
+        <v>220785</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,17 +708,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>715140</v>
+        <v>715165</v>
       </c>
       <c r="R2" t="n">
-        <v>6381111</v>
+        <v>6381230</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -753,11 +762,6 @@
           <t>2025-01-27</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Även spridd.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -769,7 +773,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -787,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122363059</v>
+        <v>122363027</v>
       </c>
       <c r="B3" t="n">
-        <v>106525</v>
+        <v>100506</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221849</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>715216</v>
+        <v>715165</v>
       </c>
       <c r="R3" t="n">
-        <v>6381161</v>
+        <v>6381230</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -867,7 +871,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Även spridd.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,7 +885,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -899,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122363018</v>
+        <v>122363017</v>
       </c>
       <c r="B4" t="n">
-        <v>106525</v>
+        <v>106528</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>715152</v>
+        <v>715169</v>
       </c>
       <c r="R4" t="n">
-        <v>6381113</v>
+        <v>6381129</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1014,7 +1018,7 @@
         <v>122363020</v>
       </c>
       <c r="B5" t="n">
-        <v>99765</v>
+        <v>99768</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1132,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122362584</v>
+        <v>122363059</v>
       </c>
       <c r="B6" t="n">
-        <v>57399</v>
+        <v>106528</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,46 +1152,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>221849</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>715124</v>
+        <v>715216</v>
       </c>
       <c r="R6" t="n">
-        <v>6381128</v>
+        <v>6381161</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,7 +1216,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Hackspår efter födosök i gran.</t>
+          <t>Även spridd.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,6 +1227,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1248,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122363027</v>
+        <v>122362584</v>
       </c>
       <c r="B7" t="n">
-        <v>100503</v>
+        <v>57399</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,41 +1260,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>715165</v>
+        <v>715124</v>
       </c>
       <c r="R7" t="n">
-        <v>6381230</v>
+        <v>6381128</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1328,7 +1337,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Hackspår efter födosök i gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,11 +1348,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1363,7 +1367,7 @@
         <v>122363025</v>
       </c>
       <c r="B8" t="n">
-        <v>98215</v>
+        <v>98218</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1481,10 +1485,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122363029</v>
+        <v>122363019</v>
       </c>
       <c r="B9" t="n">
-        <v>105899</v>
+        <v>106528</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1493,20 +1497,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220785</v>
+        <v>221849</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1514,26 +1518,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>715165</v>
+        <v>715140</v>
       </c>
       <c r="R9" t="n">
-        <v>6381230</v>
+        <v>6381111</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1568,6 +1563,11 @@
           <t>2025-01-27</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Även spridd.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1597,10 +1597,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122363017</v>
+        <v>122363016</v>
       </c>
       <c r="B10" t="n">
-        <v>106525</v>
+        <v>106528</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1637,10 +1637,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>715169</v>
+        <v>715199</v>
       </c>
       <c r="R10" t="n">
-        <v>6381129</v>
+        <v>6381142</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122363016</v>
+        <v>122363018</v>
       </c>
       <c r="B11" t="n">
-        <v>106525</v>
+        <v>106528</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>715199</v>
+        <v>715152</v>
       </c>
       <c r="R11" t="n">
-        <v>6381142</v>
+        <v>6381113</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 1719-2025 artfynd.xlsx
+++ b/artfynd/A 1719-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122363029</v>
+        <v>122363016</v>
       </c>
       <c r="B2" t="n">
-        <v>105902</v>
+        <v>106528</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>221849</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,26 +708,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>715165</v>
+        <v>715199</v>
       </c>
       <c r="R2" t="n">
-        <v>6381230</v>
+        <v>6381142</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -762,6 +753,11 @@
           <t>2025-01-27</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Även spridd.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -773,7 +769,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -791,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122363027</v>
+        <v>122363025</v>
       </c>
       <c r="B3" t="n">
-        <v>100506</v>
+        <v>98218</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,34 +803,48 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>715165</v>
+        <v>715113</v>
       </c>
       <c r="R3" t="n">
-        <v>6381230</v>
+        <v>6381204</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -867,11 +877,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,7 +908,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122363017</v>
+        <v>122363019</v>
       </c>
       <c r="B4" t="n">
         <v>106528</v>
@@ -943,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>715169</v>
+        <v>715140</v>
       </c>
       <c r="R4" t="n">
-        <v>6381129</v>
+        <v>6381111</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1015,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122363020</v>
+        <v>122362584</v>
       </c>
       <c r="B5" t="n">
-        <v>99768</v>
+        <v>57399</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,25 +1032,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>783</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1053,9 +1058,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1070,7 +1075,7 @@
         <v>6381128</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,7 +1109,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Tre strån.</t>
+          <t>Hackspår efter födosök i gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,11 +1120,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, död ved, i svacka mellan kalkryggar.</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1248,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122362584</v>
+        <v>122363017</v>
       </c>
       <c r="B7" t="n">
-        <v>57399</v>
+        <v>106528</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,46 +1264,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>221849</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>715124</v>
+        <v>715169</v>
       </c>
       <c r="R7" t="n">
-        <v>6381128</v>
+        <v>6381129</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1337,7 +1328,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Hackspår efter födosök i gran.</t>
+          <t>Även spridd.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,6 +1339,11 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1364,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122363025</v>
+        <v>122363020</v>
       </c>
       <c r="B8" t="n">
-        <v>98218</v>
+        <v>99768</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,25 +1372,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1407,21 +1403,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715113</v>
+        <v>715124</v>
       </c>
       <c r="R8" t="n">
-        <v>6381204</v>
+        <v>6381128</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1456,6 +1447,11 @@
           <t>2025-01-27</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Tre strån.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1467,7 +1463,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, död ved, i svacka mellan kalkryggar.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1485,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122363019</v>
+        <v>122363027</v>
       </c>
       <c r="B9" t="n">
-        <v>106528</v>
+        <v>100506</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1497,25 +1493,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221849</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1525,10 +1521,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>715140</v>
+        <v>715165</v>
       </c>
       <c r="R9" t="n">
-        <v>6381111</v>
+        <v>6381230</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1565,7 +1561,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Även spridd.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1579,7 +1575,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1597,10 +1593,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122363016</v>
+        <v>122363029</v>
       </c>
       <c r="B10" t="n">
-        <v>106528</v>
+        <v>105902</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1609,20 +1605,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221849</v>
+        <v>220785</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1630,17 +1626,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>715199</v>
+        <v>715165</v>
       </c>
       <c r="R10" t="n">
-        <v>6381142</v>
+        <v>6381230</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1675,11 +1680,6 @@
           <t>2025-01-27</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Även spridd.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>

--- a/artfynd/A 1719-2025 artfynd.xlsx
+++ b/artfynd/A 1719-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122363016</v>
+        <v>122363019</v>
       </c>
       <c r="B2" t="n">
-        <v>106528</v>
+        <v>106529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>715199</v>
+        <v>715140</v>
       </c>
       <c r="R2" t="n">
-        <v>6381142</v>
+        <v>6381111</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122363025</v>
+        <v>122362584</v>
       </c>
       <c r="B3" t="n">
-        <v>98218</v>
+        <v>57400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,14 +825,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -841,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>715113</v>
+        <v>715124</v>
       </c>
       <c r="R3" t="n">
-        <v>6381204</v>
+        <v>6381128</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,6 +874,11 @@
           <t>2025-01-27</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hackspår efter födosök i gran.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -887,11 +887,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -908,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122363019</v>
+        <v>122363059</v>
       </c>
       <c r="B4" t="n">
-        <v>106528</v>
+        <v>106529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -948,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>715140</v>
+        <v>715216</v>
       </c>
       <c r="R4" t="n">
-        <v>6381111</v>
+        <v>6381161</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1020,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122362584</v>
+        <v>122363025</v>
       </c>
       <c r="B5" t="n">
-        <v>57399</v>
+        <v>98219</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,25 +1027,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1058,9 +1053,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1069,13 +1069,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>715124</v>
+        <v>715113</v>
       </c>
       <c r="R5" t="n">
-        <v>6381128</v>
+        <v>6381204</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1107,11 +1107,6 @@
           <t>2025-01-27</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hackspår efter födosök i gran.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1120,6 +1115,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1136,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122363059</v>
+        <v>122363020</v>
       </c>
       <c r="B6" t="n">
-        <v>106528</v>
+        <v>99769</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,38 +1148,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221849</v>
+        <v>783</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>715216</v>
+        <v>715124</v>
       </c>
       <c r="R6" t="n">
-        <v>6381161</v>
+        <v>6381128</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1216,7 +1225,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Även spridd.</t>
+          <t>Tre strån.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,7 +1239,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
+          <t>Kalkbarrskog, död ved, i svacka mellan kalkryggar.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1248,10 +1257,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122363017</v>
+        <v>122363016</v>
       </c>
       <c r="B7" t="n">
-        <v>106528</v>
+        <v>106529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1288,10 +1297,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>715169</v>
+        <v>715199</v>
       </c>
       <c r="R7" t="n">
-        <v>6381129</v>
+        <v>6381142</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1360,10 +1369,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122363020</v>
+        <v>122363029</v>
       </c>
       <c r="B8" t="n">
-        <v>99768</v>
+        <v>105903</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1372,25 +1381,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>783</v>
+        <v>220785</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1409,10 +1418,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715124</v>
+        <v>715165</v>
       </c>
       <c r="R8" t="n">
-        <v>6381128</v>
+        <v>6381230</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1447,11 +1456,6 @@
           <t>2025-01-27</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Tre strån.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1463,7 +1467,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, död ved, i svacka mellan kalkryggar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1481,10 +1485,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122363027</v>
+        <v>122363018</v>
       </c>
       <c r="B9" t="n">
-        <v>100506</v>
+        <v>106529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1493,25 +1497,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>221849</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1521,10 +1525,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>715165</v>
+        <v>715152</v>
       </c>
       <c r="R9" t="n">
-        <v>6381230</v>
+        <v>6381113</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1561,7 +1565,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Även spridd.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,7 +1579,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1593,10 +1597,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122363029</v>
+        <v>122363017</v>
       </c>
       <c r="B10" t="n">
-        <v>105902</v>
+        <v>106529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,20 +1609,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220785</v>
+        <v>221849</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1626,26 +1630,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>715165</v>
+        <v>715169</v>
       </c>
       <c r="R10" t="n">
-        <v>6381230</v>
+        <v>6381129</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1680,6 +1675,11 @@
           <t>2025-01-27</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Även spridd.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122363018</v>
+        <v>122363027</v>
       </c>
       <c r="B11" t="n">
-        <v>106528</v>
+        <v>100507</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,25 +1721,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221849</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>715152</v>
+        <v>715165</v>
       </c>
       <c r="R11" t="n">
-        <v>6381113</v>
+        <v>6381230</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Även spridd.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 1719-2025 artfynd.xlsx
+++ b/artfynd/A 1719-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122363019</v>
+        <v>122363017</v>
       </c>
       <c r="B2" t="n">
-        <v>106529</v>
+        <v>106532</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>715140</v>
+        <v>715169</v>
       </c>
       <c r="R2" t="n">
-        <v>6381111</v>
+        <v>6381129</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122362584</v>
+        <v>122363020</v>
       </c>
       <c r="B3" t="n">
-        <v>57400</v>
+        <v>99772</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>783</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,9 +825,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -842,7 +842,7 @@
         <v>6381128</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Hackspår efter födosök i gran.</t>
+          <t>Tre strån.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,6 +887,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, död ved, i svacka mellan kalkryggar.</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -903,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122363059</v>
+        <v>122363029</v>
       </c>
       <c r="B4" t="n">
-        <v>106529</v>
+        <v>105906</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,20 +920,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221849</v>
+        <v>220785</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -936,17 +941,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>715216</v>
+        <v>715165</v>
       </c>
       <c r="R4" t="n">
-        <v>6381161</v>
+        <v>6381230</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,11 +995,6 @@
           <t>2025-01-27</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Även spridd.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -997,7 +1006,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1015,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122363025</v>
+        <v>122363019</v>
       </c>
       <c r="B5" t="n">
-        <v>98219</v>
+        <v>106532</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,52 +1036,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>221849</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>715113</v>
+        <v>715140</v>
       </c>
       <c r="R5" t="n">
-        <v>6381204</v>
+        <v>6381111</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1107,6 +1102,11 @@
           <t>2025-01-27</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Även spridd.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122363020</v>
+        <v>122362584</v>
       </c>
       <c r="B6" t="n">
-        <v>99769</v>
+        <v>57400</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,25 +1148,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>783</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1174,9 +1174,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1191,7 +1191,7 @@
         <v>6381128</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Tre strån.</t>
+          <t>Hackspår efter födosök i gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,11 +1236,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, död ved, i svacka mellan kalkryggar.</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1257,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122363016</v>
+        <v>122363018</v>
       </c>
       <c r="B7" t="n">
-        <v>106529</v>
+        <v>106532</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1297,10 +1292,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>715199</v>
+        <v>715152</v>
       </c>
       <c r="R7" t="n">
-        <v>6381142</v>
+        <v>6381113</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1369,10 +1364,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122363029</v>
+        <v>122363027</v>
       </c>
       <c r="B8" t="n">
-        <v>105903</v>
+        <v>100510</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,37 +1376,28 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220785</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
@@ -1454,6 +1440,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1485,10 +1476,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122363018</v>
+        <v>122363025</v>
       </c>
       <c r="B9" t="n">
-        <v>106529</v>
+        <v>98222</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1497,38 +1488,52 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221849</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>715152</v>
+        <v>715113</v>
       </c>
       <c r="R9" t="n">
-        <v>6381113</v>
+        <v>6381204</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1563,11 +1568,6 @@
           <t>2025-01-27</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Även spridd.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1597,10 +1597,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122363017</v>
+        <v>122363016</v>
       </c>
       <c r="B10" t="n">
-        <v>106529</v>
+        <v>106532</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1637,10 +1637,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>715169</v>
+        <v>715199</v>
       </c>
       <c r="R10" t="n">
-        <v>6381129</v>
+        <v>6381142</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122363027</v>
+        <v>122363059</v>
       </c>
       <c r="B11" t="n">
-        <v>100507</v>
+        <v>106532</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,25 +1721,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>221849</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>715165</v>
+        <v>715216</v>
       </c>
       <c r="R11" t="n">
-        <v>6381230</v>
+        <v>6381161</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Även spridd.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 1719-2025 artfynd.xlsx
+++ b/artfynd/A 1719-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122363017</v>
+        <v>122363016</v>
       </c>
       <c r="B2" t="n">
         <v>106532</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>715169</v>
+        <v>715199</v>
       </c>
       <c r="R2" t="n">
-        <v>6381129</v>
+        <v>6381142</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122363020</v>
+        <v>122363027</v>
       </c>
       <c r="B3" t="n">
-        <v>99772</v>
+        <v>100510</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,47 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>783</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>715124</v>
+        <v>715165</v>
       </c>
       <c r="R3" t="n">
-        <v>6381128</v>
+        <v>6381230</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -876,7 +867,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Tre strån.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +881,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, död ved, i svacka mellan kalkryggar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -908,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122363029</v>
+        <v>122363059</v>
       </c>
       <c r="B4" t="n">
-        <v>105906</v>
+        <v>106532</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,20 +911,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220785</v>
+        <v>221849</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -941,26 +932,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>715165</v>
+        <v>715216</v>
       </c>
       <c r="R4" t="n">
-        <v>6381230</v>
+        <v>6381161</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -995,6 +977,11 @@
           <t>2025-01-27</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Även spridd.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1006,7 +993,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1024,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122363019</v>
+        <v>122363029</v>
       </c>
       <c r="B5" t="n">
-        <v>106532</v>
+        <v>105906</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,20 +1023,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221849</v>
+        <v>220785</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1057,17 +1044,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>715140</v>
+        <v>715165</v>
       </c>
       <c r="R5" t="n">
-        <v>6381111</v>
+        <v>6381230</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1102,11 +1098,6 @@
           <t>2025-01-27</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Även spridd.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1118,7 +1109,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1136,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122362584</v>
+        <v>122363025</v>
       </c>
       <c r="B6" t="n">
-        <v>57400</v>
+        <v>98222</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,25 +1139,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1174,9 +1165,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1185,13 +1181,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>715124</v>
+        <v>715113</v>
       </c>
       <c r="R6" t="n">
-        <v>6381128</v>
+        <v>6381204</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1223,11 +1219,6 @@
           <t>2025-01-27</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Hackspår efter födosök i gran.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1236,6 +1227,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1252,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122363018</v>
+        <v>122363020</v>
       </c>
       <c r="B7" t="n">
-        <v>106532</v>
+        <v>99772</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,38 +1260,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221849</v>
+        <v>783</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>715152</v>
+        <v>715124</v>
       </c>
       <c r="R7" t="n">
-        <v>6381113</v>
+        <v>6381128</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1332,7 +1337,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Även spridd.</t>
+          <t>Tre strån.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,7 +1351,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
+          <t>Kalkbarrskog, död ved, i svacka mellan kalkryggar.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1364,10 +1369,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122363027</v>
+        <v>122363019</v>
       </c>
       <c r="B8" t="n">
-        <v>100510</v>
+        <v>106532</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,25 +1381,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>221849</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1404,10 +1409,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715165</v>
+        <v>715140</v>
       </c>
       <c r="R8" t="n">
-        <v>6381230</v>
+        <v>6381111</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1444,7 +1449,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Även spridd.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,7 +1463,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1476,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122363025</v>
+        <v>122363018</v>
       </c>
       <c r="B9" t="n">
-        <v>98222</v>
+        <v>106532</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1488,52 +1493,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>221849</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>715113</v>
+        <v>715152</v>
       </c>
       <c r="R9" t="n">
-        <v>6381204</v>
+        <v>6381113</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1568,6 +1559,11 @@
           <t>2025-01-27</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Även spridd.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1579,7 +1575,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1597,10 +1593,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122363016</v>
+        <v>122362584</v>
       </c>
       <c r="B10" t="n">
-        <v>106532</v>
+        <v>57400</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1613,37 +1609,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221849</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ganthem Kumble 1:12 (3) O vägen, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>715199</v>
+        <v>715124</v>
       </c>
       <c r="R10" t="n">
-        <v>6381142</v>
+        <v>6381128</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1677,7 +1682,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Även spridd.</t>
+          <t>Hackspår efter födosök i gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,11 +1693,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Kalkglänta i kalkbarrskog/alvarskog.</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1709,7 +1709,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122363059</v>
+        <v>122363017</v>
       </c>
       <c r="B11" t="n">
         <v>106532</v>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>715216</v>
+        <v>715169</v>
       </c>
       <c r="R11" t="n">
-        <v>6381161</v>
+        <v>6381129</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 1719-2025 artfynd.xlsx
+++ b/artfynd/A 1719-2025 artfynd.xlsx
@@ -1369,7 +1369,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122363019</v>
+        <v>122363018</v>
       </c>
       <c r="B8" t="n">
         <v>106532</v>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715140</v>
+        <v>715152</v>
       </c>
       <c r="R8" t="n">
-        <v>6381111</v>
+        <v>6381113</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1481,7 +1481,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122363018</v>
+        <v>122363019</v>
       </c>
       <c r="B9" t="n">
         <v>106532</v>
@@ -1521,10 +1521,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>715152</v>
+        <v>715140</v>
       </c>
       <c r="R9" t="n">
-        <v>6381113</v>
+        <v>6381111</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 1719-2025 artfynd.xlsx
+++ b/artfynd/A 1719-2025 artfynd.xlsx
@@ -1369,7 +1369,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122363018</v>
+        <v>122363019</v>
       </c>
       <c r="B8" t="n">
         <v>106532</v>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715152</v>
+        <v>715140</v>
       </c>
       <c r="R8" t="n">
-        <v>6381113</v>
+        <v>6381111</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1481,7 +1481,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122363019</v>
+        <v>122363018</v>
       </c>
       <c r="B9" t="n">
         <v>106532</v>
@@ -1521,10 +1521,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>715140</v>
+        <v>715152</v>
       </c>
       <c r="R9" t="n">
-        <v>6381111</v>
+        <v>6381113</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 1719-2025 artfynd.xlsx
+++ b/artfynd/A 1719-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1819,6 +1819,536 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123800890</v>
+      </c>
+      <c r="B12" t="n">
+        <v>89615</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>245042</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Besk kastanjemusseron</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tricholoma batschii</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Mort. Chr. &amp; Noordel.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Rasneskogen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>715054</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6381103</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ganthem</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-27</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-27</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ÅGP grupp kalkbarrskog </t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123800888</v>
+      </c>
+      <c r="B13" t="n">
+        <v>86407</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Rasneskogen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>714987</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6381032</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ganthem</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-27</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-27</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ÅGP grupp kalkbarrskog </t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123800889</v>
+      </c>
+      <c r="B14" t="n">
+        <v>90760</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Rasneskogen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>715001</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6381093</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ganthem</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-27</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-27</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ÅGP grupp kalkbarrskog </t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>123800892</v>
+      </c>
+      <c r="B15" t="n">
+        <v>88330</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>510</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Rasneskogen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>715097</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6381017</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ganthem</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-27</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-27</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ÅGP grupp kalkbarrskog </t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>123800891</v>
+      </c>
+      <c r="B16" t="n">
+        <v>86407</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Rasneskogen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>715101</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6381010</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ganthem</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-27</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-27</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ÅGP grupp kalkbarrskog </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 1719-2025 artfynd.xlsx
+++ b/artfynd/A 1719-2025 artfynd.xlsx
@@ -1821,10 +1821,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123800890</v>
+        <v>123800891</v>
       </c>
       <c r="B12" t="n">
-        <v>89615</v>
+        <v>86412</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1833,25 +1833,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>245042</v>
+        <v>248956</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1861,10 +1861,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>715054</v>
+        <v>715101</v>
       </c>
       <c r="R12" t="n">
-        <v>6381103</v>
+        <v>6381010</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1930,7 +1930,7 @@
         <v>123800888</v>
       </c>
       <c r="B13" t="n">
-        <v>86407</v>
+        <v>86412</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123800889</v>
+        <v>123800892</v>
       </c>
       <c r="B14" t="n">
-        <v>90760</v>
+        <v>88335</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2045,25 +2045,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2015</v>
+        <v>510</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>715001</v>
+        <v>715097</v>
       </c>
       <c r="R14" t="n">
-        <v>6381093</v>
+        <v>6381017</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2139,10 +2139,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123800892</v>
+        <v>123800890</v>
       </c>
       <c r="B15" t="n">
-        <v>88330</v>
+        <v>89620</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2151,25 +2151,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>510</v>
+        <v>245042</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2179,10 +2179,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>715097</v>
+        <v>715054</v>
       </c>
       <c r="R15" t="n">
-        <v>6381017</v>
+        <v>6381103</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2245,10 +2245,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123800891</v>
+        <v>123800889</v>
       </c>
       <c r="B16" t="n">
-        <v>86407</v>
+        <v>90765</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2261,21 +2261,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>248956</v>
+        <v>2015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>715101</v>
+        <v>715001</v>
       </c>
       <c r="R16" t="n">
-        <v>6381010</v>
+        <v>6381093</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 1719-2025 artfynd.xlsx
+++ b/artfynd/A 1719-2025 artfynd.xlsx
@@ -1821,10 +1821,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123800891</v>
+        <v>123800888</v>
       </c>
       <c r="B12" t="n">
-        <v>86412</v>
+        <v>86414</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1861,10 +1861,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>715101</v>
+        <v>714987</v>
       </c>
       <c r="R12" t="n">
-        <v>6381010</v>
+        <v>6381032</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1927,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123800888</v>
+        <v>123800891</v>
       </c>
       <c r="B13" t="n">
-        <v>86412</v>
+        <v>86414</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>714987</v>
+        <v>715101</v>
       </c>
       <c r="R13" t="n">
-        <v>6381032</v>
+        <v>6381010</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123800892</v>
+        <v>123800890</v>
       </c>
       <c r="B14" t="n">
-        <v>88335</v>
+        <v>89622</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2045,25 +2045,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>510</v>
+        <v>245042</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>715097</v>
+        <v>715054</v>
       </c>
       <c r="R14" t="n">
-        <v>6381017</v>
+        <v>6381103</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2139,10 +2139,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123800890</v>
+        <v>123800889</v>
       </c>
       <c r="B15" t="n">
-        <v>89620</v>
+        <v>90767</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2151,25 +2151,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>245042</v>
+        <v>2015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2179,10 +2179,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>715054</v>
+        <v>715001</v>
       </c>
       <c r="R15" t="n">
-        <v>6381103</v>
+        <v>6381093</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2245,10 +2245,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123800889</v>
+        <v>123800892</v>
       </c>
       <c r="B16" t="n">
-        <v>90765</v>
+        <v>88337</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2257,25 +2257,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2015</v>
+        <v>510</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>715001</v>
+        <v>715097</v>
       </c>
       <c r="R16" t="n">
-        <v>6381093</v>
+        <v>6381017</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 1719-2025 artfynd.xlsx
+++ b/artfynd/A 1719-2025 artfynd.xlsx
@@ -1927,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123800891</v>
+        <v>123800892</v>
       </c>
       <c r="B13" t="n">
-        <v>86414</v>
+        <v>88337</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1939,25 +1939,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>248956</v>
+        <v>510</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>715101</v>
+        <v>715097</v>
       </c>
       <c r="R13" t="n">
-        <v>6381010</v>
+        <v>6381017</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2245,10 +2245,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123800892</v>
+        <v>123800891</v>
       </c>
       <c r="B16" t="n">
-        <v>88337</v>
+        <v>86414</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2257,25 +2257,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>510</v>
+        <v>248956</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>715097</v>
+        <v>715101</v>
       </c>
       <c r="R16" t="n">
-        <v>6381017</v>
+        <v>6381010</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 1719-2025 artfynd.xlsx
+++ b/artfynd/A 1719-2025 artfynd.xlsx
@@ -1821,7 +1821,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123800888</v>
+        <v>123800891</v>
       </c>
       <c r="B12" t="n">
         <v>86414</v>
@@ -1861,10 +1861,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>714987</v>
+        <v>715101</v>
       </c>
       <c r="R12" t="n">
-        <v>6381032</v>
+        <v>6381010</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1927,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123800892</v>
+        <v>123800889</v>
       </c>
       <c r="B13" t="n">
-        <v>88337</v>
+        <v>90767</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1939,25 +1939,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>510</v>
+        <v>2015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>715097</v>
+        <v>715001</v>
       </c>
       <c r="R13" t="n">
-        <v>6381017</v>
+        <v>6381093</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123800890</v>
+        <v>123800892</v>
       </c>
       <c r="B14" t="n">
-        <v>89622</v>
+        <v>88337</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2045,25 +2045,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>245042</v>
+        <v>510</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>715054</v>
+        <v>715097</v>
       </c>
       <c r="R14" t="n">
-        <v>6381103</v>
+        <v>6381017</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2139,10 +2139,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123800889</v>
+        <v>123800888</v>
       </c>
       <c r="B15" t="n">
-        <v>90767</v>
+        <v>86414</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2155,21 +2155,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2015</v>
+        <v>248956</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2179,10 +2179,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>715001</v>
+        <v>714987</v>
       </c>
       <c r="R15" t="n">
-        <v>6381093</v>
+        <v>6381032</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2245,10 +2245,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123800891</v>
+        <v>123800890</v>
       </c>
       <c r="B16" t="n">
-        <v>86414</v>
+        <v>89622</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2257,25 +2257,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>248956</v>
+        <v>245042</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>715101</v>
+        <v>715054</v>
       </c>
       <c r="R16" t="n">
-        <v>6381010</v>
+        <v>6381103</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 1719-2025 artfynd.xlsx
+++ b/artfynd/A 1719-2025 artfynd.xlsx
@@ -1821,10 +1821,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123800891</v>
+        <v>123800890</v>
       </c>
       <c r="B12" t="n">
-        <v>86414</v>
+        <v>89622</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1833,25 +1833,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>248956</v>
+        <v>245042</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1861,10 +1861,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>715101</v>
+        <v>715054</v>
       </c>
       <c r="R12" t="n">
-        <v>6381010</v>
+        <v>6381103</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1927,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123800889</v>
+        <v>123800891</v>
       </c>
       <c r="B13" t="n">
-        <v>90767</v>
+        <v>86414</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1943,21 +1943,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2015</v>
+        <v>248956</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>715001</v>
+        <v>715101</v>
       </c>
       <c r="R13" t="n">
-        <v>6381093</v>
+        <v>6381010</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123800892</v>
+        <v>123800889</v>
       </c>
       <c r="B14" t="n">
-        <v>88337</v>
+        <v>90767</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2045,25 +2045,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>510</v>
+        <v>2015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>715097</v>
+        <v>715001</v>
       </c>
       <c r="R14" t="n">
-        <v>6381017</v>
+        <v>6381093</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2245,10 +2245,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123800890</v>
+        <v>123800892</v>
       </c>
       <c r="B16" t="n">
-        <v>89622</v>
+        <v>88337</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2257,25 +2257,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>245042</v>
+        <v>510</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>715054</v>
+        <v>715097</v>
       </c>
       <c r="R16" t="n">
-        <v>6381103</v>
+        <v>6381017</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 1719-2025 artfynd.xlsx
+++ b/artfynd/A 1719-2025 artfynd.xlsx
@@ -1821,10 +1821,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123800890</v>
+        <v>123800892</v>
       </c>
       <c r="B12" t="n">
-        <v>89622</v>
+        <v>88337</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1833,25 +1833,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>245042</v>
+        <v>510</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1861,10 +1861,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>715054</v>
+        <v>715097</v>
       </c>
       <c r="R12" t="n">
-        <v>6381103</v>
+        <v>6381017</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123800889</v>
+        <v>123800888</v>
       </c>
       <c r="B14" t="n">
-        <v>90767</v>
+        <v>86414</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2015</v>
+        <v>248956</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>715001</v>
+        <v>714987</v>
       </c>
       <c r="R14" t="n">
-        <v>6381093</v>
+        <v>6381032</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2139,10 +2139,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123800888</v>
+        <v>123800890</v>
       </c>
       <c r="B15" t="n">
-        <v>86414</v>
+        <v>89622</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2151,25 +2151,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>248956</v>
+        <v>245042</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2179,10 +2179,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>714987</v>
+        <v>715054</v>
       </c>
       <c r="R15" t="n">
-        <v>6381032</v>
+        <v>6381103</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2245,10 +2245,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123800892</v>
+        <v>123800889</v>
       </c>
       <c r="B16" t="n">
-        <v>88337</v>
+        <v>90767</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2257,25 +2257,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>510</v>
+        <v>2015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>715097</v>
+        <v>715001</v>
       </c>
       <c r="R16" t="n">
-        <v>6381017</v>
+        <v>6381093</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 1719-2025 artfynd.xlsx
+++ b/artfynd/A 1719-2025 artfynd.xlsx
@@ -1821,10 +1821,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123800892</v>
+        <v>123800891</v>
       </c>
       <c r="B12" t="n">
-        <v>88337</v>
+        <v>86414</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1833,25 +1833,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>510</v>
+        <v>248956</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1861,10 +1861,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>715097</v>
+        <v>715101</v>
       </c>
       <c r="R12" t="n">
-        <v>6381017</v>
+        <v>6381010</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123800891</v>
+        <v>123800888</v>
       </c>
       <c r="B13" t="n">
         <v>86414</v>
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>715101</v>
+        <v>714987</v>
       </c>
       <c r="R13" t="n">
-        <v>6381010</v>
+        <v>6381032</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123800888</v>
+        <v>123800890</v>
       </c>
       <c r="B14" t="n">
-        <v>86414</v>
+        <v>89622</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2045,25 +2045,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>248956</v>
+        <v>245042</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>714987</v>
+        <v>715054</v>
       </c>
       <c r="R14" t="n">
-        <v>6381032</v>
+        <v>6381103</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2139,10 +2139,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123800890</v>
+        <v>123800889</v>
       </c>
       <c r="B15" t="n">
-        <v>89622</v>
+        <v>90767</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2151,25 +2151,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>245042</v>
+        <v>2015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2179,10 +2179,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>715054</v>
+        <v>715001</v>
       </c>
       <c r="R15" t="n">
-        <v>6381103</v>
+        <v>6381093</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2245,10 +2245,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123800889</v>
+        <v>123800892</v>
       </c>
       <c r="B16" t="n">
-        <v>90767</v>
+        <v>88337</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2257,25 +2257,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2015</v>
+        <v>510</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>715001</v>
+        <v>715097</v>
       </c>
       <c r="R16" t="n">
-        <v>6381093</v>
+        <v>6381017</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 1719-2025 artfynd.xlsx
+++ b/artfynd/A 1719-2025 artfynd.xlsx
@@ -1927,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123800890</v>
+        <v>123800892</v>
       </c>
       <c r="B13" t="n">
-        <v>89644</v>
+        <v>88359</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1939,25 +1939,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>245042</v>
+        <v>510</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>715054</v>
+        <v>715097</v>
       </c>
       <c r="R13" t="n">
-        <v>6381103</v>
+        <v>6381017</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2139,10 +2139,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123800892</v>
+        <v>123800890</v>
       </c>
       <c r="B15" t="n">
-        <v>88359</v>
+        <v>89644</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2151,25 +2151,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>510</v>
+        <v>245042</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2179,10 +2179,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>715097</v>
+        <v>715054</v>
       </c>
       <c r="R15" t="n">
-        <v>6381017</v>
+        <v>6381103</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 1719-2025 artfynd.xlsx
+++ b/artfynd/A 1719-2025 artfynd.xlsx
@@ -1821,10 +1821,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123800889</v>
+        <v>123800891</v>
       </c>
       <c r="B12" t="n">
-        <v>90789</v>
+        <v>86436</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1837,21 +1837,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2015</v>
+        <v>248956</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1861,10 +1861,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>715001</v>
+        <v>715101</v>
       </c>
       <c r="R12" t="n">
-        <v>6381093</v>
+        <v>6381010</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123800888</v>
+        <v>123800889</v>
       </c>
       <c r="B14" t="n">
-        <v>86436</v>
+        <v>90789</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>248956</v>
+        <v>2015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>714987</v>
+        <v>715001</v>
       </c>
       <c r="R14" t="n">
-        <v>6381032</v>
+        <v>6381093</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2245,7 +2245,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123800891</v>
+        <v>123800888</v>
       </c>
       <c r="B16" t="n">
         <v>86436</v>
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>715101</v>
+        <v>714987</v>
       </c>
       <c r="R16" t="n">
-        <v>6381010</v>
+        <v>6381032</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
